--- a/text/foundationScores/milkywayvodka_3_seconds_MFT_MAC.xlsx
+++ b/text/foundationScores/milkywayvodka_3_seconds_MFT_MAC.xlsx
@@ -425,166 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AI56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>chunkEnd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chunkStart</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>V_neu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>V_neg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>V_pos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>V_com</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_virtue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_virtue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_virtue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_virtue</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_vice</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_vice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_vice</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_vice</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_vice</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_moral_nonmoral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_virtue</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_virtue</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_virtue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_virtue</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_virtue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_virtue</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_vice</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_vice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_vice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_vice</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_vice</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_vice</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_vice</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_moral_nonmoral</t>
         </is>
@@ -594,104 +604,114 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24.395</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>21.192</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>79.60000000000001</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>20.4</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>31.82</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve"> She took a deep breath and tried to calm down.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.06751607525601333</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.004219409282700422</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.1107561230909708</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0916169084942699</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.04861111111111111</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.07517049669732478</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.05968377313690573</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1.5</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.05967078189300411</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>0.05087719298245614</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.04824561403508772</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.1279703934553954</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.03603603603603604</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>0.07034883720930232</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>0.09261287574540587</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.1467864923747277</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
         <v>0.1558730158730159</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>0.1587987355110643</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>0.03125</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>0.1006645114942529</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>0.05769230769230769</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -699,104 +719,114 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>32.984</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>24.415</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>22.2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>57.19</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve"> The situation seemed too good, and after she spent most of the last week's worrying, she knew she could enjoy the moment.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.03931644359464628</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.04451398767188242</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.03483623548922057</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.02259659532386805</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.0362937210282343</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.06811938581786932</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.06225714490458262</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.05340901771336554</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.05372142461092729</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.05535077278774758</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.06273504273504274</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.02803030303030303</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.04995016671033501</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.04586735762144054</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.06817812960376006</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>0.06413007399762367</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>0.02771194472067557</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>0.05658877063343869</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>0.1331079807239766</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>0.06131380136355261</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>0.0625416223809996</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.02287581699346405</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.01418439716312057</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>0.04135430637279603</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -804,73 +834,77 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>38.029</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>34.285</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>63.7</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>15.9</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>20.4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>17.79</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve"> She looked at her reflection in the mirror and started laughing uncontrollably.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.04320987654320987</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.05319148936170213</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.02873563218390804</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.03645833333333334</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.03626943005181347</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.04373144553551039</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.03333333333333334</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.0456989247311828</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.02577319587628866</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.5</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>0.12</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
@@ -881,27 +915,33 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0.1232876712328767</v>
       </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0.09876543209876543</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>0.07339449541284404</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>0.1159420289855072</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.1232876712328767</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.180327868852459</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -909,104 +949,114 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>46.677</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>39.75</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>83.8</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>16.2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>47.67</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve"> That evening, at her biggest moment of triumph, she did the expected, calling her mother to brag.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.03889552635072348</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.1234289340593887</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.06288619235606688</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.05044802867383512</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0.08229187479557466</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.08579963235294118</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.05604619565217391</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.003731343283582089</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.0304320987654321</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.1377922779238569</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.1284465234465235</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>0.07233044733044733</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>0.1227370307698472</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.1066952970994086</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.1437334217506631</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>0.09384399074467267</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1014,104 +1064,114 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>64.638</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>48.108</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>79.10000000000001</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>20.9</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>84.39</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve"> In general, conversations with her mother resembled an intense and unbelievably optimistic lecture about all the good things she had accomplished in her life, starting from how she managed to slide from her mother's womb up to the way she had reached the finals in American Idol.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.01845872684782819</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.01186757215619695</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.04207808901354725</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.0243364072822835</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.02537568099109601</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.0950238218354264</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.06462573677697044</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.03910538347996902</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.0277310039258831</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.0425691818650799</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>1.2</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.05361907569829085</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.09086364100550888</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.04081041369176962</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.07344504314784933</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.09726792438315338</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.08046058949574013</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>0.01539400515394005</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>0.08029036982289016</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>0.06252078723988837</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>0.06857216857216858</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>0.06152032894833291</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>0.05613149952772594</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.1227698571978813</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.04904439052490812</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.6923076923076923</v>
       </c>
     </row>
@@ -1119,104 +1179,114 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>69.627</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>66.622</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>55.60000000000001</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>44.4</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>68.08</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve"> To be honest, it wasn't far from the truth.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.07040441176470588</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.1184635470349756</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.03968253968253969</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0741869918699187</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.09606090698444224</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.02724795640326975</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.03858784893267652</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.06222222222222223</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.03414634146341463</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.01955034213098729</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.2395251396648045</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.1115569823434992</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.1627906976744186</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.1528966425279789</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.05357142857142857</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>0.1857142857142857</v>
       </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
       <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
         <v>0.04516129032258064</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.06993006993006994</v>
       </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0.04814814814814815</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1224,67 +1294,71 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>73.007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>69.843</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>75.8</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>24.2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>49.39</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve"> Her mother had gone through only two hours of relaxed labor.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.02235772357723577</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.06980143470732421</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.02252252252252252</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.1000181834526495</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.05522890597517462</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.03846153846153847</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.02288647342995169</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.04934777364212848</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>1.5</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
@@ -1292,36 +1366,42 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>0.1097643097643098</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.04307001428863033</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>0.03125</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>0.1992867202762255</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>0.1555925155925156</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>0.1045991045991046</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>0.1042253521126761</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.05031446540880503</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.1724137931034483</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.06895943562610229</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1329,104 +1409,114 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>78.013</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>73.548</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>79.5</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>20.5</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>-47.67</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve"> She could imagine, though she never actually tried, it could have gone worse.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.02283653846153846</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.0474702380952381</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.02548543689320388</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.05591630591630592</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>0.01704545454545454</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.08546615626351661</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.05871709218165911</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.0775995691467003</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.01413690476190476</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.05905517779466696</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.06201550387596899</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.03065134099616858</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>0.2284731153681265</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>0.02898550724637681</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>0.2076585077654274</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>0.1625541579315164</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>0.1320634920634921</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>0.08956796628029505</v>
       </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
         <v>0.09195402298850575</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.09578754578754578</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1434,104 +1524,114 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>86.824</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>79.455</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>61.5</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>38.5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>92.94</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve"> But to this day, every time she looked at her mom's belly, she felt that it was a safe haven that truly felt nice and warm.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.07064203016932062</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.0504234251840271</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.06131520259532827</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.03332299115142157</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>0.04673721340388007</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>0.0401367854301662</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.01318506278927149</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.04136064030131827</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>0.02201217047445996</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.05147945052466717</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>4.5</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0.1801118435880099</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>0.1506186511813976</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.06257203493678429</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>0.06527190118684219</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>0.05648093728000207</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>0.1340398731970562</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.05686724309310145</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>0.02800550060824033</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>0.005208333333333333</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>0.01724137931034483</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>0.06925270880195239</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.1167688842012058</v>
       </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0.01738241308793456</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -1539,104 +1639,114 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>93.572</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>88.946</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>100</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve"> As for Idle, it wasn't that simple, as nothing in life ever is.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.0425531914893617</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0.072744014732965</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>0.1211651368560324</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.1271335341365462</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.03614457831325301</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>0.09061587147030185</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.01162790697674418</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.1948786507610037</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
         <v>0.1202185792349727</v>
       </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.1656804733727811</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
         <v>0.1508224617129892</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
         <v>0.08974358974358974</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.1016483516483516</v>
       </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0.07339901477832513</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1644,104 +1754,114 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>106.084</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>93.923</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>72</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>28</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>91.86</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve"> She did pick a great song, and well, she did take it for granted, although it was better than anything she could ever hope for, and she could go on and on and on about all the things that worked out.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.04616019794490687</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.08704600223777563</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.07279225199083143</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.0777369241574639</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.04905559312316705</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.04552695412910467</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.02432183355371239</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.02067183462532299</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.03039113880235375</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.03771949551170331</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.08890662249973159</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.1320426048958858</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.09243194568404949</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.064203478875643</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>0.1815582742774954</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>0.06508315196742068</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>0.09352381358825539</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>0.02614626752557787</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>0.02688172043010753</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>0.04814814814814814</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>0.07534244771086876</v>
       </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
         <v>0.05634920634920635</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.006756756756756757</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1749,104 +1869,114 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>117.062</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>107.025</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>82.39999999999999</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>17.6</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>-81.26000000000001</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">  But it was beside the point.  She learned her lesson, or so she told everyone, not understanding what the lesson was and how the hell was she supposed to learn it.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.0216998191681736</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.0376658753527938</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.03463885861627846</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>0.0198565128142593</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.06013851205277966</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.06135867241220187</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.03580279239251689</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.0270251286996676</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.06696735700031289</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>3.5</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.08513210108604845</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>0.1338077866805637</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>0.0852935137766984</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>0.02941176470588236</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>0.1052345807146015</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Z13" t="n">
         <v>0.07480192416525185</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>0.05302033151054833</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>0.03933963288801998</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>0.01908396946564886</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.09121982209385306</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.03944444444444444</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.0515878897672376</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.03950617283950617</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1854,104 +1984,114 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>124.8</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>118.51</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>55.60000000000001</v>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>44.4</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>90.41</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Her mom recognized her elated mood and said to her enthusiastically, I'm so proud of you, Rachel.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.06539036544850499</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.03515379786566227</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.0666668385947629</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.02545454545454545</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.02978723404255319</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.008844439089046873</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.009457769694213938</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.02670525010334849</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.0549303683737646</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.08291128888288041</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.0625</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.2631578947368421</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>0.06</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>0.1388888888888889</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.09375</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>0.03542234332425068</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.03963221306277743</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>0.04338771259979174</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>0.03931080628972901</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
         <v>0.0333696046427276</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.02737752161383285</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>0.01955888472742405</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1959,104 +2099,114 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>131.891</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>124.86</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>79.5</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>20.5</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>-65.97</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Listen to me.  This might sound a bit obnoxious, but have you forgone the idea of seeing a psychic about your stage fright?</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.07410833225439846</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.06438865496783146</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.03900044447930556</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.05568253968253969</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>0.02944359562006621</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>0.0301357257878997</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.01639344262295082</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.01794871794871795</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>0.0303109713487072</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.05780652480193219</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>1.5</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.07602684808704528</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>0.1953208556149733</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>0.08342767295597484</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.1083465959328028</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.04942716857610475</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>0.04027531688701104</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>0.06398046398046398</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
       <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
         <v>0.0722943722943723</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0.008695652173913044</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
         <v>0.02105263157894737</v>
       </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2064,104 +2214,114 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>137.66</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>133.333</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>63.4</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>36.6</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>69.67999999999999</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Wow, mom, that was just a fleeting idea.  I'm not that desperate.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.04813218390804597</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.01234567901234568</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.02914389799635701</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0.0231729055258467</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.06060606060606061</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.04626660558863949</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>0.04580712788259959</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.07886904761904762</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>1.5</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
         <v>0.1494252873563219</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>0.06593406593406594</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
       <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
         <v>0.1948051948051948</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -2169,104 +2329,114 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>145.733</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>138.602</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>89.2</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>10.8</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>29.24</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">  Bambi, I know you aren't.  She sometimes hated her mom for her random comments, but she had a point.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.015625</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.01606875934230194</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.06082352060258074</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.01223491027732463</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.04726137928195928</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.03550664451827243</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.0211864406779661</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.05002130941267199</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.0744896417230306</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.08913240548178958</v>
       </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
         <v>0.06352657004830918</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
       <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.03581267217630854</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>0.02419354838709678</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>0.0425531914893617</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>0.1320228104722561</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>0.04301075268817204</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
         <v>0.1362446072273739</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>0.1035075136612022</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>0.03985507246376812</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AH17" t="n">
         <v>0.02210884353741497</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -2274,104 +2444,114 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>154.272</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>146.675</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>73.5</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>18</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>8.5</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>-38.18</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sure, Mom, I'm done with that, she said hesitantly as she hung up and thought to herself, what do I have to lose?</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.03771739130434783</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.03222431703079369</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.04915056075598846</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.01764705882352941</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.01075268817204301</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.04463592033507358</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.0411244363608806</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.0391713747645951</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.04477588569725549</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.07893409507964277</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>2.5</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.04207920792079208</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.03645833333333334</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.05357142857142857</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.08510436432637571</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>0.08071095571095571</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>0.04032258064516129</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>0.03805719091673675</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>0.1450835319935875</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>0.1343774173136297</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>0.1037076256630628</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
         <v>0.03156016504962641</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AF18" t="n">
         <v>0.1045226401592017</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AG18" t="n">
         <v>0.0897148802099015</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AH18" t="n">
         <v>0.08120801379228346</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
         <v>1.333333333333333</v>
       </c>
     </row>
@@ -2379,73 +2559,77 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>163.873</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>156.617</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>73.5</v>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>26.5</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>75.79000000000001</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve"> She woke up late the next morning and calmly scanned the newspaper for the combination of best and nearest psychic.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.008375209380234507</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.03100775193798449</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.0425531914893617</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.03053847905282331</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.02166643551692786</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.04374967378255649</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>0.02173823115744188</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>0.08247422680412371</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
         <v>0.09259259259259259</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
@@ -2453,30 +2637,36 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
       <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
         <v>0.05833333333333333</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>0.07920792079207921</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>0.06976744186046512</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>0.1411764705882353</v>
       </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -2484,104 +2674,114 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>170.529</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>164.123</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>77.2</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>5.7</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>17.1</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>58.59</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve"> Before long, she understood that, knowing nothing about the subject, it was hard to figure out which psychic was the best.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.02811584403876493</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.05964213754137709</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.0483124908585637</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.02439024390243902</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>0.01709401709401709</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0.06154616017184733</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>0.04640023315282791</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.05500509911868526</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>0.07987952217279405</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.06390556255718637</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>0.1047248803827751</v>
       </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
         <v>0.08732558139534885</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>0.1087914023960536</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>0.1090025457070123</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>0.05965532479010163</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>0.02649006622516556</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>0.09166022419791264</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.1615316316118627</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>0.09785289424053387</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>0.06419457735247208</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>0.1035137701804368</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AG20" t="n">
         <v>0.03246753246753246</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AH20" t="n">
         <v>0.0297661233167966</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2589,88 +2789,92 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>179.338</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>171.27</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>83.7</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>16.3</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>62.49</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">  She would have to settle for the nearest one she could find.  Hermione the Great, pedicurist and fortune teller, money back guaranteed.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.03115264797507788</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.02815315315315315</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.06713352007469654</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.05473986047529063</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>0.02205882352941177</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>0.05803500397772474</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0.1647566357109926</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.01626016260162602</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.08476190476190476</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.5</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.2105319913731128</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.1785048151954627</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.1468637992831541</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>0.08431050149279565</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>0.1940476190476191</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.1499157776530039</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>0.02873563218390805</v>
       </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
@@ -2684,9 +2888,15 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.188953488372093</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -2694,104 +2904,114 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>188.587</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>179.398</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>20.6</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>75.73999999999999</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve"> The combination was kind of intriguing, and just the thought of Harry Potter, which was her all-time favorite book by far, made the choice even more exciting.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.01684636118598383</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.07477922265559374</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.07272257111768321</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.06625708994743494</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>0.0370245316908905</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0.0459062289042944</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>0.02798383048028201</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.02118561710398445</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>0.02596202551075227</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.02811891800351968</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>1.4</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.03820879703232644</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>0.101873787331572</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>0.04652272894176398</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.08202597734056838</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.09778049562102718</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.09697883281550207</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>0.03152709359605912</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>0.1210478039953713</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.0634954193093728</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>0.0962175092730297</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>0.02787427626137304</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>0.07056197990518065</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>0.02985074626865672</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.04687265601903771</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2799,104 +3019,114 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>193.999</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>189.908</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>63.3</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
         <v>36.7</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>70.03</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">  A sweet voice answered her call.  It's your lucky day, Ms. Monroe.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.05714285714285713</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.06593406593406592</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0.04117647058823529</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.004297994269340974</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>0.05022254104374195</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.05509183312425617</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.0007800312012480499</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>0.4</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
         <v>0.1264024326308063</v>
       </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
         <v>0.05412218268090154</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.006437768240343348</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>0.2296525096525097</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.1018318965517241</v>
       </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
         <v>0.09094076655052265</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.09259259259259259</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2904,104 +3134,114 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>203.232</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>194.86</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>77.8</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>11.3</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>10.9</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>21.86</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Somehow a fake name felt sexier.  I have a place at 5.30 p.m. today, but it's going to be rainy, so be sure to bring an umbrella.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.02101449275362319</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.05031553135420667</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.0339814554210839</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.02847399829497016</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>0.02604390681003584</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.09579182879126219</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>0.08395404085059256</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.0756395762036685</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.06131195428761518</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.08387846720729231</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>1.2</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.1415438011192424</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.1007827985477382</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.1022417582417582</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>0.05161290322580645</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>0.1521436290865276</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.1165898718937622</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.03237514518002323</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>0.06761073977568824</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>0.08552771855010662</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>0.06863816774025636</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>0.1234326551243622</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>0.05660377358490566</v>
       </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.04533397289842907</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -3009,104 +3249,114 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>213.608</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>204.955</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>57.8</v>
       </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>42.2</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>90.81</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve"> She arrived at Hermione's clinic at 5.36, and Hermione, who to her delight was a surprisingly beautiful magician, welcomed her in.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.2027704096669614</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.02191091954022988</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.1359675183204595</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0692055692055692</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.103136874444175</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>0.004901960784313725</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
         <v>0.5</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.21875</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.117816091954023</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.07894736842105263</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>0.1071428571428571</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>0.02</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
       <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -3114,104 +3364,114 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>220.017</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>214.509</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>58.2</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
         <v>41.8</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">  I love Tuesdays, she said.  For some reason, everyone seems to be happy.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.07802795031055901</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.03197509903791737</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.1024307704656758</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.03447204968944099</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.02494443775019748</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.02682221211776742</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.02770295209199637</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.03046635676438086</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.1424688057040998</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0706238693054109</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>0.0938597352177801</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>0.07280801825293351</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>0.1133474576271186</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.1500159489633174</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>0.03368673050615595</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>0.01771117166212534</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>0.01981610653138871</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.02169385629989587</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>0.0196554031448645</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>0.05547790576963967</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>0.01368876080691643</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>0.04008247266674233</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3219,104 +3479,114 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>227.333</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>221.144</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>83.3</v>
       </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>16.7</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>45.88</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">  I know what you mean.  I used to be in the phone book industry, Rachel replied, feeling that was a satisfactory response.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.01219512195121951</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.01807597810110417</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.03546423810150915</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.04869494172598601</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.03713113467910909</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.1017709814925622</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.05002508877111794</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.03995052566481139</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>0.007078507078507079</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.04642333444611373</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>2.333333333333333</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.06731999053651119</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.03517406962785114</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.06534695131296793</v>
       </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>0.06218699601052543</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>0.04986622773865712</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>0.04737854737854737</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>0.08542389287730903</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>0.1160230576946312</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>0.04666872912749975</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>0.09722478116024029</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>0.09289102263402363</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>0.04278115501519757</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.05507374974129418</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>2.333333333333333</v>
       </c>
     </row>
@@ -3324,104 +3594,114 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>233.202</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>228.335</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>83.8</v>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>16.2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>40.19</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve"> So, are you interested in pedicure session, or are you just here for fortune telling?</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.1222103973168214</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>0.07481125600549073</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.06308610400682012</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.07724301841948901</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>0.05333333333333334</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
       <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>1.5</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
         <v>0.1463414634146341</v>
       </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
       <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.125</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
         <v>0.2619047619047619</v>
       </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
         <v>0.09375</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.1714285714285714</v>
       </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
       <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -3429,104 +3709,114 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>240.473</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>233.622</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>74.7</v>
       </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>25.3</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>72.69</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Hermione asked.  Just the fortune telling.  My toenails seem to be just glowing these days, thank you, Rachel said proudly.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.04434046345811051</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.05128960905699355</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.04294012706786256</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.07124811463046758</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>0.025206492257535</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.01182221211776742</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.05433448408131952</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.01137129380053908</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.03893241612376964</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>0.09529211571185479</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.02531645569620253</v>
       </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.07593457943925234</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>0.009259259259259259</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>0.07822883151936862</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>0.1486270766383778</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>0.02892514173319449</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>0.05745720419315267</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>0.1222464030951517</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>0.01825168107588857</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.03355207699776988</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -3534,88 +3824,92 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>248.164</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>241.274</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>48.1</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>12.5</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>39.4</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>68.08</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sure, darling, Hermione replied and grinned.  What seems to be bothering you, Ms. Monroe?</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.06304347826086956</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.05708661417322835</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.06127450980392156</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.06197478991596639</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.06854838709677419</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>0.103448275862069</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>0.01388888888888889</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.03030303030303031</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.1683168316831683</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.1458333333333333</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.2580645161290323</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>0.1612903225806452</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.04878048780487805</v>
       </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
@@ -3632,6 +3926,12 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
         <v>0.1428571428571428</v>
       </c>
     </row>
@@ -3639,34 +3939,38 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>253.809</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>249.022</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>87.3</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>12.7</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>22.35</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">  It's Simon, the meanest judge in American Idol.  I can't stop thinking about him.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
@@ -3677,66 +3981,72 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.1081217049663138</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>0.1005424242584084</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.09945857746164762</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>0.1288904863722382</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.09942680776014108</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>0.75</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.03558383409921056</v>
       </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
         <v>0.1556530214424951</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>0.07938697318007663</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>0.1748892120204958</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>0.1557926667021446</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>0.1376283846872082</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>0.0308641975308642</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>0.07392905332980239</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -3744,104 +4054,114 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>258.555</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>254.75</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>74.5</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>25.5</v>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
         <v>-66.52</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve"> I am supposed to participate in the final, but I am afraid to panic.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.03017241379310345</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>0.06056540358865941</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.01744186046511628</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>0.006756756756756758</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.05533088235294118</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>0.1012652130435843</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.03873239436619718</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>0.061084142394822</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.08300967511025932</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>4</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.01736111111111111</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.04069767441860465</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>0.1623597756410256</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.01209677419354839</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>0.07631578947368421</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.05964912280701754</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.004166666666666667</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>0.1291383701188455</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>0.1535353535353535</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>0.2131410256410256</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>0.0576923076923077</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>0.02127659574468085</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.1525641025641026</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3849,104 +4169,114 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>266.887</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>259.477</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>0.18</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">  I'm absolutely obsessed with him.  I dream about him constantly, and I imagine his voice in almost every man I hear.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.03945037796647954</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.04728008715006739</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.06614362788363314</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.03300229182582124</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.03767747236115716</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.05451879789818231</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.06821039536497499</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.02476197524859776</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>0.086037882876131</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.07540843390074396</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>7</v>
       </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
       <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
         <v>0.09632034632034632</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>0.0375</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.07509157509157507</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>0.1914144736842105</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>0.2260007350975675</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>0.05772151898734177</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>0.09415323632191101</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>0.0879416282642089</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>0.03205128205128205</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AH33" t="n">
         <v>0.08279264666125979</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AI33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3954,104 +4284,114 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>270.873</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>266.927</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>75.2</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>24.8</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>51.06</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve"> To be honest, you are the first person I've confided with.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.0703125</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.09183673469387756</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.05952380952380953</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.04878048780487805</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0.02830188679245283</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.08266129032258064</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.0703971119133574</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.05275229357798166</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.06904761904761905</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>2</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.1703703703703704</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.226890756302521</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>0.2038834951456311</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.1</v>
       </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
       <c r="AA34" t="n">
         <v>0</v>
       </c>
       <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
         <v>0.1570247933884298</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>0.1065573770491803</v>
       </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
       <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4059,104 +4399,114 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>283.127</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>272.375</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
         <v>12.9</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>51.13</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">  Do you like vodka, Ms. Monroe?  Rachel didn't understand the relevance of the question, but she replied nevertheless, I'm not crazy about it, but I drink a sip now and then.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.01841564342510953</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.001319894408447324</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.03987619652509256</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.05805986351576695</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.03882587375410342</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.07584618636787034</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.08456875448293887</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.02491582491582492</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>0.005747126436781608</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.05309139784946237</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>1</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.03325842162213582</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>0.03259505352528608</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>0.03447472629862567</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.02874018553684537</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>0.06463467358408992</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.006561679790026247</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>0.03180354267310789</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>0.02347417840375587</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>0.02150537634408602</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>0.03888888888888889</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AE35" t="n">
         <v>0.04301075268817204</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AF35" t="n">
         <v>0.03300330033003301</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>0.0430172068827531</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AH35" t="n">
         <v>0.03787878787878788</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -4164,104 +4514,114 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>292.384</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>283.187</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>89.3</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
         <v>10.7</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>45.88</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve"> Just keep your eyes on the vodka bottle, Hermione said, as she started to gently caress a tiny vodka bottle which was standing on the table.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.02806231327358088</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.03799363023797947</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.02901329243353783</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.04323671497584541</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.06860685737822426</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.05038153049026714</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.05033851055356432</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>0.06957454799790098</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.02798180046927118</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>0.05</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>0.1345882352941176</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
         <v>0.01923076923076923</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>0.02962962962962963</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
         <v>0.04379310344827586</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AB36" t="n">
         <v>0.179199142383729</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>0.01585288522511097</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>0.08710817145966979</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>0.1612171750868325</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>0.1086574597754046</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AG36" t="n">
         <v>0.1022752095587752</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AH36" t="n">
         <v>0.05601033978267354</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.625</v>
       </c>
     </row>
@@ -4269,104 +4629,114 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>297.574</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>293.566</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>84.5</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>15.5</v>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
         <v>-29.6</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">  Aren't you supposed to do that with a crystal ball?  Rachel asked doubtfully.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.05</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.02227722772277228</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.03333333333333334</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
         <v>0.02830188679245283</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.0569620253164557</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.03291139240506329</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>0.03883495145631068</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.09838444687842279</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.5</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
         <v>0.08139534883720931</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>0.2043828264758497</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.0379746835443038</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>0.1</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.1040334481062469</v>
       </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
         <v>0.1625660652451248</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>0.05235602094240838</v>
       </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
         <v>0.05128205128205128</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AF37" t="n">
         <v>0.06428571428571428</v>
       </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0.1307692307692308</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4374,49 +4744,53 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>302.529</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>298.685</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>63.8</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
         <v>36.2</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>62.49</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve"> Put your trust in Hermione and everything will be just fine."</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.1639344262295082</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.1274509803921569</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.1916666666666667</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>0.2061068702290076</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>0.1415929203539823</v>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
@@ -4427,35 +4801,35 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
         <v>0.5</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.2258064516129032</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>0.3170731707317073</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>0.3230769230769231</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>0.25</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>0.1794871794871795</v>
       </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
@@ -4472,6 +4846,12 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4479,104 +4859,114 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>313.14</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>303.57</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>71.3</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>20.4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>50.06</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">  She took a deep breath and tried not to laugh.  The next thing she remembered was looking around and feeling like she could really use a good pedicure session.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.02790597184156044</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>0.03091766894398466</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.05143201429706136</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.03888635014796693</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.03123065627456211</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.07940583606383064</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.05644997073886064</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.04527696594185956</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.04540552717835619</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.04283041779820836</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>2.5</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.05835580807002056</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.05193423127939652</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.04545938683365584</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.03121966470792453</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0.08873199155563471</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>0.04525148290596484</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>0.04494139939022228</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>0.1141626668735103</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>0.1021229754431359</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>0.1014993513344338</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AE39" t="n">
         <v>0.1031922925800367</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AF39" t="n">
         <v>0.04403108465608466</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AG39" t="n">
         <v>0.07213321281209212</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AH39" t="n">
         <v>0.06306231651409316</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -4584,104 +4974,114 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>318.646</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>313.981</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>82.89999999999999</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>17.1</v>
       </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
         <v>-47.67</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve"> When she left Hermione's clinic an hour later, she felt worse than she had for ages.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>0.04586161387631976</v>
       </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
         <v>0.09083652417461108</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.03984614909008471</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.0773165592005413</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.05593732723382935</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>0.06495272332729271</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>0.1079500786163522</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.05696202531645569</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.03627622377622378</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.05447316931018692</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>0.06853146853146853</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>0.004464285714285714</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>0.08866995073891626</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>0.07674877454758455</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>0.04655172413793104</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.05063291139240506</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.1289461921578066</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.01458333333333333</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>0.04807056560678007</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4689,104 +5089,114 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>325.333</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>319.667</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>62.5</v>
       </c>
-      <c r="C41" t="n">
+      <c r="E41" t="n">
         <v>26.3</v>
       </c>
-      <c r="D41" t="n">
+      <c r="F41" t="n">
         <v>11.2</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>-52.66999999999999</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">  It was like a nightmare.  Her face looked pale and she had severe pain in her throat.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>0.01923883783532906</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>0.001583873290136789</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>0.04868799905628646</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>0.01279389186273289</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>0.01701248313090419</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>0.1704984927578855</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>0.09130660975121722</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>0.032</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>0.04996739093124636</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>0.06351799242424241</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
         <v>0.005767012687427913</v>
       </c>
-      <c r="T41" t="n">
+      <c r="V41" t="n">
         <v>0.06884206374489904</v>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>0.006172839506172839</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>0.00329489291598023</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>0.06840115192683945</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>0.006561679790026247</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>0.004025764895330112</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>0.117816091954023</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>0.05128205128205129</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>0.1031909418425116</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>0.1043591565979626</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>0.04545454545454545</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.04519774011299435</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -4794,104 +5204,114 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>330.514</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>326.208</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>84.8</v>
       </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
         <v>15.2</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
         <v>36.12</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve"> As she strolled down the street, she heard a man that sounded exactly like Simon.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>0.02387269543722319</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>0.01462735155100635</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.002966958867161159</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.01948145717098786</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>0.03432155534200488</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>0.05148769577964836</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>0.0429727235067531</v>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
         <v>0.06717543217809493</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>0.05472366598989307</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>0.02734177215189874</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.04608315843212888</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.06365959621773574</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.02084656084656085</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0.01549044926310165</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>0.02326272008398279</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>0.01536557930258718</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>0.002415458937198068</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AB42" t="n">
         <v>0.08073331592007313</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>0.08495419309372798</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>0.07463079421184364</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>0.03944197844007609</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.08610421836228288</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.07715617715617715</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>0.04824739921472062</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -4899,34 +5319,38 @@
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>334.54</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>331.295</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="C43" t="n">
+      <c r="E43" t="n">
         <v>24.4</v>
       </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
         <v>-44.04</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve"> And after another second, she realized that she was panicking.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
@@ -4937,29 +5361,29 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
         <v>0.1463414634146341</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>0.05714285714285713</v>
       </c>
-      <c r="O43" t="n">
+      <c r="Q43" t="n">
         <v>0.06521739130434782</v>
       </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="S43" t="n">
         <v>0.1063829787234043</v>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
@@ -4997,6 +5421,12 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5004,104 +5434,114 @@
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>341.209</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>335.681</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>65.5</v>
       </c>
-      <c r="C44" t="n">
+      <c r="E44" t="n">
         <v>25.6</v>
       </c>
-      <c r="D44" t="n">
+      <c r="F44" t="n">
         <v>8.9</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
         <v>-42.15</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve"> Feeling stressed, she stopped to buy a vodka martini and continued walking home heavy-hearted.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>0.0202275600505689</v>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>0.01815980629539951</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>0.02097044779971609</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>0.04867434279198984</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>0.1017008727373149</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>0.09588227385942756</v>
       </c>
-      <c r="O44" t="n">
+      <c r="Q44" t="n">
         <v>0.07555824543912738</v>
       </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
         <v>0.06939487083263216</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="S44" t="n">
         <v>0.0370415982484948</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>1.75</v>
       </c>
-      <c r="S44" t="n">
+      <c r="U44" t="n">
         <v>0.09866365647305649</v>
       </c>
-      <c r="T44" t="n">
+      <c r="V44" t="n">
         <v>0.02674897119341564</v>
       </c>
-      <c r="U44" t="n">
+      <c r="W44" t="n">
         <v>0.07202944916123211</v>
       </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
         <v>0.04901960784313725</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
         <v>0.09394274141581516</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Z44" t="n">
         <v>0.0746104135407618</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AA44" t="n">
         <v>0.08574929971988797</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>0.1549991879105803</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AC44" t="n">
         <v>0.125048859643022</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>0.06597701149425288</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>0.1110192115045501</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>0.0740209210358464</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.06174242424242424</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
         <v>0.07217151962914674</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AI44" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -5109,104 +5549,114 @@
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>346.717</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>342.511</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>100</v>
       </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve"> As days went by, she noticed that she was thinking about Simon more than ever.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>0.034</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
         <v>0.06434653043848446</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>0.02054794520547945</v>
       </c>
-      <c r="O45" t="n">
+      <c r="Q45" t="n">
         <v>0.0671641791044776</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>0.0807057057057057</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="S45" t="n">
         <v>0.1040202966432475</v>
       </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
         <v>0.08823529411764706</v>
       </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.06097560975609756</v>
       </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
         <v>0.08333333333333334</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
         <v>0.09745762711864407</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>0.1101190476190476</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AE45" t="n">
         <v>0.1911483253588517</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AF45" t="n">
         <v>0.1309523809523809</v>
       </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
         <v>0.0939982347749338</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AI45" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -5214,104 +5664,114 @@
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>356.13</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>347.438</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>77.5</v>
       </c>
-      <c r="C46" t="n">
+      <c r="E46" t="n">
         <v>14.5</v>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
         <v>8.1</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
         <v>-43.91</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">  She was completely terrified of meeting Simon.  She called her mom and easily persuaded her to come with her to the finals the next day.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>0.05933400118098468</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>0.01051755447941889</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>0.06823823567724976</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>0.04016801768212323</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>0.03118939443110275</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>0.02260626798037509</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>0.04616312598067419</v>
       </c>
-      <c r="O46" t="n">
+      <c r="Q46" t="n">
         <v>0.02902383076334905</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
         <v>0.0369255187719918</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="S46" t="n">
         <v>0.04461761025654893</v>
       </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>1.75</v>
       </c>
-      <c r="S46" t="n">
+      <c r="U46" t="n">
         <v>0.02032520325203252</v>
       </c>
-      <c r="T46" t="n">
+      <c r="V46" t="n">
         <v>0.06403177370919307</v>
       </c>
-      <c r="U46" t="n">
+      <c r="W46" t="n">
         <v>0.04111193534843467</v>
       </c>
-      <c r="V46" t="n">
+      <c r="X46" t="n">
         <v>0.009157509157509158</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Y46" t="n">
         <v>0.06050989372244672</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Z46" t="n">
         <v>0.02169625246548323</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AA46" t="n">
         <v>0.04240787619891861</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AB46" t="n">
         <v>0.1286190667481142</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>0.0661789193039193</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AD46" t="n">
         <v>0.09974849176718829</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="n">
         <v>0.1132571869895822</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.05099121193541795</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AG46" t="n">
         <v>0.01522842639593909</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AH46" t="n">
         <v>0.02020849354866273</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -5319,67 +5779,71 @@
       <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>359.6</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>356.397</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>100</v>
       </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve"> When she arrived at the studios, Simon was staring at his feet.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>0.1025641025641026</v>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>0.08080808080808081</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
         <v>0.01470588235294117</v>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
         <v>0.25</v>
       </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
@@ -5387,36 +5851,42 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
       <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
         <v>0.125</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AC47" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AD47" t="n">
         <v>0.04</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AE47" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
       <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
         <v>0.07407407407407407</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AI47" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5424,104 +5894,114 @@
       <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>365.846</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>360.961</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>86.7</v>
       </c>
-      <c r="C48" t="n">
+      <c r="E48" t="n">
         <v>13.3</v>
       </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
         <v>-31.97</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve">  How are you doing, Simon?  she asked, almost losing control over her voice for a moment.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>0.02285714285714285</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>0.00891089108910891</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>0.01333333333333334</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>0.03582542694497154</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>0.0890399919222763</v>
       </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
         <v>0.07923726036564453</v>
       </c>
-      <c r="O48" t="n">
+      <c r="Q48" t="n">
         <v>0.07978994932801391</v>
       </c>
-      <c r="P48" t="n">
+      <c r="R48" t="n">
         <v>0.08816999242151163</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="S48" t="n">
         <v>0.05900745840504876</v>
       </c>
-      <c r="R48" t="n">
+      <c r="T48" t="n">
         <v>5</v>
       </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
       <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
         <v>0.1024787817507737</v>
       </c>
-      <c r="V48" t="n">
+      <c r="X48" t="n">
         <v>0.01518987341772152</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Y48" t="n">
         <v>0.01965174129353234</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Z48" t="n">
         <v>0.09247465673000285</v>
       </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
         <v>0.264262684634255</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AC48" t="n">
         <v>0.1655382741167482</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>0.04424242424242424</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AE48" t="n">
         <v>0.1048976447281532</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AF48" t="n">
         <v>0.1039351446099912</v>
       </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
         <v>0.144417044278405</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5529,104 +6009,114 @@
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>374.795</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>367.287</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>76</v>
       </c>
-      <c r="C49" t="n">
+      <c r="E49" t="n">
         <v>8.4</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
         <v>15.6</v>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
         <v>44.04</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve">  I am doing great.  How are you these days?  Getting by, she answered, actually thinking about the bottle that she was hiding.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>0.05926565226803214</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>0.05198346698346699</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>0.05151411016365033</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>0.02820174994088038</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>0.01323529411764706</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>0.04691358024691358</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>0.0203403902034039</v>
       </c>
-      <c r="O49" t="n">
+      <c r="Q49" t="n">
         <v>0.04135206321334504</v>
       </c>
-      <c r="P49" t="n">
+      <c r="R49" t="n">
         <v>0.0510024154589372</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="S49" t="n">
         <v>0.08517235252309878</v>
       </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S49" t="n">
+      <c r="U49" t="n">
         <v>0.02115384615384616</v>
       </c>
-      <c r="T49" t="n">
+      <c r="V49" t="n">
         <v>0.07649174777824799</v>
       </c>
-      <c r="U49" t="n">
+      <c r="W49" t="n">
         <v>0.07272130532633159</v>
       </c>
-      <c r="V49" t="n">
+      <c r="X49" t="n">
         <v>0.04158354706944049</v>
       </c>
-      <c r="W49" t="n">
+      <c r="Y49" t="n">
         <v>0.08099005424954792</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Z49" t="n">
         <v>0.086034018903324</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AA49" t="n">
         <v>0.0869265864355345</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AB49" t="n">
         <v>0.1246175265651005</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AC49" t="n">
         <v>0.06332657379650855</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AD49" t="n">
         <v>0.08624999999999999</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AE49" t="n">
         <v>0.0852974828375286</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AF49" t="n">
         <v>0.07380952380952381</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AG49" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AH49" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AI49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5634,104 +6124,114 @@
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>380.4</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>375.996</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>83.8</v>
       </c>
-      <c r="C50" t="n">
+      <c r="E50" t="n">
         <v>16.2</v>
       </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
         <v>-40.19</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve">  I have to go to the dressing room.  Do you need anything?  he inquired impatiently.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>0.1062223100614325</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>0.09037586244265433</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>0.04868913857677902</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>0.08482097411551312</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>0.08292599262498927</v>
       </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
       <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
         <v>0.02406417112299465</v>
       </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
         <v>0.1241721854304636</v>
       </c>
-      <c r="T50" t="n">
+      <c r="V50" t="n">
         <v>0.1249446167478954</v>
       </c>
-      <c r="U50" t="n">
+      <c r="W50" t="n">
         <v>0.07459677419354839</v>
       </c>
-      <c r="V50" t="n">
+      <c r="X50" t="n">
         <v>0.07023411371237458</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Y50" t="n">
         <v>0.08928571428571429</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Z50" t="n">
         <v>0.1449275362318841</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AA50" t="n">
         <v>0.04320987654320987</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AB50" t="n">
         <v>0.0958904109589041</v>
       </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
         <v>0.04411764705882353</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AE50" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AD50" t="n">
+      <c r="AF50" t="n">
         <v>0.05</v>
       </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>0.05128205128205128</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -5739,104 +6239,114 @@
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>385.645</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>381.221</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>87.8</v>
       </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
         <v>12.2</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
         <v>20.23</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve">  No, I'm fine.  I was just planning to work on the routine, she replied.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>0.02582781456953642</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>0.03258145363408521</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>0.0234375</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>0.03180438842203548</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>0.04033411336453458</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>0.09229637057643787</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>0.04370915032679738</v>
       </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
         <v>0.04913209767578699</v>
       </c>
-      <c r="P51" t="n">
+      <c r="R51" t="n">
         <v>0.0518236683285227</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="S51" t="n">
         <v>0.03444272445820434</v>
       </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>4</v>
       </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
         <v>0.1136363636363636</v>
       </c>
-      <c r="U51" t="n">
+      <c r="W51" t="n">
         <v>0.1049382716049383</v>
       </c>
-      <c r="V51" t="n">
+      <c r="X51" t="n">
         <v>0.1138888888888889</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Y51" t="n">
         <v>0.08947368421052632</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Z51" t="n">
         <v>0.1957264957264957</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AA51" t="n">
         <v>0.09269882659713169</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AB51" t="n">
         <v>0.2408088235294118</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AC51" t="n">
         <v>0.07352941176470588</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
         <v>0.1363636363636364</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AE51" t="n">
         <v>0.06578947368421052</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AF51" t="n">
         <v>0.1296296296296296</v>
       </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
       <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -5844,88 +6354,92 @@
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>389.051</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>385.928</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>86.7</v>
       </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
         <v>13.3</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
         <v>25</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve"> By the way, do you have a vodka martini on you by any chance?</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>0.0708955223880597</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>0.05405405405405406</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>0.04347826086956521</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>0.05</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>0.049079754601227</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>0.060849598163031</v>
       </c>
-      <c r="O52" t="n">
+      <c r="Q52" t="n">
         <v>0.04221491228070175</v>
       </c>
-      <c r="P52" t="n">
+      <c r="R52" t="n">
         <v>0.03282275711159737</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="S52" t="n">
         <v>0.05606860158311346</v>
       </c>
-      <c r="R52" t="n">
+      <c r="T52" t="n">
         <v>1</v>
       </c>
-      <c r="S52" t="n">
+      <c r="U52" t="n">
         <v>0.1506578947368421</v>
       </c>
-      <c r="T52" t="n">
+      <c r="V52" t="n">
         <v>0.2256747670732879</v>
       </c>
-      <c r="U52" t="n">
+      <c r="W52" t="n">
         <v>0.2017670393076091</v>
       </c>
-      <c r="V52" t="n">
+      <c r="X52" t="n">
         <v>0.1200249092976661</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Y52" t="n">
         <v>0.1572479764532745</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Z52" t="n">
         <v>0.1550760523523169</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AA52" t="n">
         <v>0.04411764705882353</v>
       </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
@@ -5939,9 +6453,15 @@
         <v>0</v>
       </c>
       <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>0.0509433962264151</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5949,40 +6469,44 @@
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>393.576</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>389.712</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>72.89999999999999</v>
       </c>
-      <c r="C53" t="n">
+      <c r="E53" t="n">
         <v>27.1</v>
       </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
         <v>-38.18</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t xml:space="preserve">  What?  No, he answered, looking at her blamefully.</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>0.07943925233644859</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>0.102880658436214</v>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
@@ -5993,60 +6517,66 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
         <v>0.09787234042553193</v>
       </c>
-      <c r="P53" t="n">
+      <c r="R53" t="n">
         <v>0.07531380753138077</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="S53" t="n">
         <v>0.065</v>
       </c>
-      <c r="R53" t="n">
+      <c r="T53" t="n">
         <v>0.5</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
       <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
         <v>0.125</v>
       </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
         <v>0.09230769230769231</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AB53" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AC53" t="n">
         <v>0.1443298969072165</v>
       </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
         <v>0.1573033707865168</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AF53" t="n">
         <v>0.140625</v>
       </c>
-      <c r="AE53" t="n">
+      <c r="AG53" t="n">
         <v>0.1384615384615385</v>
       </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6054,104 +6584,114 @@
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>401.404</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>394.697</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>86.2</v>
       </c>
-      <c r="C54" t="n">
+      <c r="E54" t="n">
         <v>4.100000000000001</v>
       </c>
-      <c r="D54" t="n">
+      <c r="F54" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
         <v>35.35</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rachel felt like a little girl.  I'm sorry, I'll be back in a jiffy, she said as she ran to find a hidden spot.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>0.01542634996582365</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>0.04214257372796927</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>0.03902922833560056</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>0.03237985566904406</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>0.03327581043139138</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>0.05855074227161451</v>
       </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
         <v>0.03548230540748032</v>
       </c>
-      <c r="O54" t="n">
+      <c r="Q54" t="n">
         <v>0.03852768279297535</v>
       </c>
-      <c r="P54" t="n">
+      <c r="R54" t="n">
         <v>0.02997229818049995</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="S54" t="n">
         <v>0.03527200980718711</v>
       </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>0.09785123325348238</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>0.09585129004949564</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>0.01908831908831909</v>
       </c>
-      <c r="V54" t="n">
+      <c r="X54" t="n">
         <v>0.01601202346888638</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Y54" t="n">
         <v>0.03363539028020786</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Z54" t="n">
         <v>0.05222310773906298</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AA54" t="n">
         <v>0.005986887508626639</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AB54" t="n">
         <v>0.05115523869956329</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AC54" t="n">
         <v>0.01585288522511097</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AD54" t="n">
         <v>0.07713769373556886</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AE54" t="n">
         <v>0.07086479797127906</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AF54" t="n">
         <v>0.09320742939548507</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AG54" t="n">
         <v>0.02761767531219981</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AH54" t="n">
         <v>0.05513204250380606</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -6159,104 +6699,114 @@
       <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>410.334</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>402.425</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>100</v>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t xml:space="preserve"> On her way to the stage, while licking what was left of her drink, she thought to herself, why didn't I go to a regular psychologist first?</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>0.01633986928104575</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>0.01958943201693823</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>0.0373634673976695</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>0.08954861334828584</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>0.07370734392290872</v>
       </c>
-      <c r="O55" t="n">
+      <c r="Q55" t="n">
         <v>0.0391699182460052</v>
       </c>
-      <c r="P55" t="n">
+      <c r="R55" t="n">
         <v>0.06962070889782061</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="S55" t="n">
         <v>0.08380072629727631</v>
       </c>
-      <c r="R55" t="n">
+      <c r="T55" t="n">
         <v>3</v>
       </c>
-      <c r="S55" t="n">
+      <c r="U55" t="n">
         <v>0.107406015037594</v>
       </c>
-      <c r="T55" t="n">
+      <c r="V55" t="n">
         <v>0.04964294758166624</v>
       </c>
-      <c r="U55" t="n">
+      <c r="W55" t="n">
         <v>0.07184978756453012</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>0.093103526734088</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Y55" t="n">
         <v>0.05999320767532688</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Z55" t="n">
         <v>0.07293951185001768</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AA55" t="n">
         <v>0.07049808429118773</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AB55" t="n">
         <v>0.06633825944170772</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AC55" t="n">
         <v>0.07677924506252191</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AD55" t="n">
         <v>0.0685666805151641</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
         <v>0.03948038716250637</v>
       </c>
-      <c r="AE55" t="n">
+      <c r="AG55" t="n">
         <v>0.03582089552238805</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AH55" t="n">
         <v>0.0493849920783523</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -6264,104 +6814,114 @@
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>416.679</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>411.335</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="C56" t="n">
+      <c r="E56" t="n">
         <v>8.6</v>
       </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
         <v>-15.11</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve">  I must never admit this to mom.  She entered the stage with a blank stare in her eyes.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="J56" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>0.0504812834224599</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>0.008</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>0.01538461538461539</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>0.08404252031766632</v>
       </c>
-      <c r="N56" t="n">
+      <c r="P56" t="n">
         <v>0.02222222222222222</v>
       </c>
-      <c r="O56" t="n">
+      <c r="Q56" t="n">
         <v>0.06612294171616205</v>
       </c>
-      <c r="P56" t="n">
+      <c r="R56" t="n">
         <v>0.05870469399881164</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="S56" t="n">
         <v>0.07043843624406285</v>
       </c>
-      <c r="R56" t="n">
+      <c r="T56" t="n">
         <v>2.5</v>
       </c>
-      <c r="S56" t="n">
+      <c r="U56" t="n">
         <v>0.009523809523809523</v>
       </c>
-      <c r="T56" t="n">
+      <c r="V56" t="n">
         <v>0.0909090909090909</v>
       </c>
-      <c r="U56" t="n">
+      <c r="W56" t="n">
         <v>0.02515723270440251</v>
       </c>
-      <c r="V56" t="n">
+      <c r="X56" t="n">
         <v>0.0665340406719717</v>
       </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
       <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
         <v>0.06002554278416347</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AB56" t="n">
         <v>0.06911928651059086</v>
       </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
         <v>0.05952380952380953</v>
       </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
         <v>0.1090909090909091</v>
       </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
       <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
         <v>0.75</v>
       </c>
     </row>
